--- a/slide_classification/SurGen_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,16 +471,16 @@
         <v>0.9038461538461539</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.87248322147651</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8903225806451613</v>
+        <v>0.901840490797546</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9051178660049628</v>
+        <v>0.8968151938027797</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +490,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5595744680851064</v>
+        <v>0.7526785714285714</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7191489361702128</v>
+        <v>0.5134920634920636</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6416666666666666</v>
+        <v>0.5864864864864865</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6522781774580335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6348594224924012</v>
+        <v>0.6262338247162887</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +512,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5796658882701635</v>
+        <v>0.7458455522971652</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7482517482517482</v>
+        <v>0.5133230187381812</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6551498494961392</v>
+        <v>0.6100478468899522</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6477806392970762</v>
+        <v>0.6836854460093896</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6577120313287819</v>
+        <v>0.638225465983672</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8778170814276438</v>
+        <v>0.9051307115823244</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9176976869284561</v>
+        <v>0.8528416478892576</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8848107197588559</v>
+        <v>0.8852848797956968</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8896794718297814</v>
+        <v>0.8986875800256081</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8925012399861842</v>
+        <v>0.8854862048232217</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8780141843971632</v>
+        <v>0.8245535714285714</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7976359338061466</v>
+        <v>0.6238095238095238</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8114285714285715</v>
+        <v>0.754954954954955</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7485714285714286</v>
+        <v>0.8095923261390888</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8089125295508275</v>
+        <v>0.7532275940830347</v>
       </c>
     </row>
     <row r="7">
@@ -578,31 +579,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[139   2]
- [ 13   2]]</t>
+          <t>[[132, 8], [7, 9]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[137   4]
- [  8   7]]</t>
+          <t>[[129, 6], [13, 1]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[133   7]
- [ 10   5]]</t>
+          <t>[[144, 4], [12, 3]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[136   4]
- [ 11   4]]</t>
+          <t>[[135, 4], [10, 5]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[[136, 4], [10, 4]]</t>
+          <t>[[135, 6], [10, 4]]</t>
         </is>
       </c>
     </row>
@@ -613,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8269230769230769</v>
+        <v>0.7628205128205128</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.7516778523489933</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8451612903225807</v>
+        <v>0.7177914110429447</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8</v>
+        <v>0.7662337662337663</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8231492969396195</v>
+        <v>0.7496308856115543</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7851063829787234</v>
+        <v>0.7017857142857142</v>
       </c>
       <c r="C9" t="n">
-        <v>0.75177304964539</v>
+        <v>0.5748677248677249</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7654761904761904</v>
+        <v>0.6049549549549549</v>
       </c>
       <c r="E9" t="n">
-        <v>0.680952380952381</v>
+        <v>0.6326139088729017</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7458270010131711</v>
+        <v>0.6285555757453238</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6731589974392799</v>
+        <v>0.6028895768833848</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6553030303030303</v>
+        <v>0.5326777994405357</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6821599453178401</v>
+        <v>0.5302005012531328</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6112774047407168</v>
+        <v>0.5702325581395349</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6554748444502168</v>
+        <v>0.559000108929147</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8542269788874896</v>
+        <v>0.8032071128046361</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8480477855477856</v>
+        <v>0.7924719798515492</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8657200185213768</v>
+        <v>0.7724295401079385</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8297063344389612</v>
+        <v>0.8039263062518877</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8494252793489033</v>
+        <v>0.7930087347540028</v>
       </c>
     </row>
     <row r="12">
@@ -701,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8491725768321513</v>
+        <v>0.7374999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7843971631205674</v>
+        <v>0.665079365079365</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8480952380952381</v>
+        <v>0.6869369369369369</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7171428571428571</v>
+        <v>0.7218225419664269</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7997019587977034</v>
+        <v>0.7028347109956822</v>
       </c>
     </row>
     <row r="13">
@@ -724,31 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[118  23]
- [  4  11]]</t>
+          <t>[[109, 31], [6, 10]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[118  23]
- [  5  10]]</t>
+          <t>[[107, 28], [9, 5]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[121  19]
- [  5  10]]</t>
+          <t>[[110, 38], [8, 7]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[116  24]
- [  7   8]]</t>
+          <t>[[111, 28], [8, 7]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[118, 22], [5, 10]]</t>
+          <t>[[109, 31], [8, 7]]</t>
         </is>
       </c>
     </row>
@@ -759,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9102564102564102</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8782051282051282</v>
+        <v>0.9060402684563759</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9096774193548387</v>
+        <v>0.8957055214723927</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8903225806451613</v>
+        <v>0.9025974025974026</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8971153846153845</v>
+        <v>0.8972396442853889</v>
       </c>
     </row>
     <row r="15">
@@ -781,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5205357142857143</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5453900709219859</v>
+        <v>0.532010582010582</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5231981981981982</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5226190476190476</v>
+        <v>0.5297362110311751</v>
       </c>
       <c r="F15" t="n">
-        <v>0.533668946301925</v>
+        <v>0.5263701763814174</v>
       </c>
     </row>
     <row r="16">
@@ -803,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5388513513513513</v>
+        <v>0.5191780821917809</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5540845494207913</v>
+        <v>0.537677304964539</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5386904761904762</v>
+        <v>0.5249442825304302</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5234219569542413</v>
+        <v>0.533050333535476</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5387620834792151</v>
+        <v>0.5287125008055565</v>
       </c>
     </row>
     <row r="17">
@@ -825,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8731159043659045</v>
+        <v>0.8523709167544783</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8611461503743737</v>
+        <v>0.8728045123518492</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8723118279569891</v>
+        <v>0.8673834823865483</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8606467949054544</v>
+        <v>0.867530892394446</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8668051694006804</v>
+        <v>0.8650224509718305</v>
       </c>
     </row>
     <row r="18">
@@ -847,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7378250591016549</v>
+        <v>0.6575892857142858</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5427895981087471</v>
+        <v>0.5912698412698414</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6971428571428572</v>
+        <v>0.5549549549549549</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5895238095238096</v>
+        <v>0.6278177458033573</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6418203309692672</v>
+        <v>0.6079079569356098</v>
       </c>
     </row>
     <row r="19">
@@ -870,26 +863,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[141   0]
- [ 14   1]]</t>
+          <t>[[137, 3], [15, 1]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[135   6]
- [ 13   2]]</t>
+          <t>[[134, 1], [13, 1]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[140   0]
- [ 14   1]]</t>
+          <t>[[145, 3], [14, 1]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[137   3]
- [ 14   1]]</t>
+          <t>[[138, 1], [14, 1]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -905,19 +894,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6794871794871795</v>
+        <v>0.697986577181208</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.6257668711656442</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.6883116883116883</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6801075268817204</v>
+        <v>0.688913720062071</v>
       </c>
     </row>
     <row r="21">
@@ -927,19 +916,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6</v>
+        <v>0.6633928571428571</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5843971631205673</v>
+        <v>0.5772486772486772</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7083333333333333</v>
+        <v>0.5842342342342342</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5894484412470025</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6071111955420466</v>
+        <v>0.6035810524681927</v>
       </c>
     </row>
     <row r="22">
@@ -949,19 +938,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.50271546635183</v>
+        <v>0.5764322563127885</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5085685483870968</v>
+        <v>0.5119021620441144</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.4814061440567464</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4763835145261348</v>
+        <v>0.5153422501966956</v>
       </c>
       <c r="F22" t="n">
-        <v>0.518583548982932</v>
+        <v>0.5212707031525863</v>
       </c>
     </row>
     <row r="23">
@@ -971,19 +960,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7241394968667696</v>
+        <v>0.7879376483775072</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7426527605459057</v>
+        <v>0.756643621083118</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7909677419354838</v>
+        <v>0.7046616871437626</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7161246733279045</v>
+        <v>0.7484749711342946</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7434711681690158</v>
+        <v>0.7494294819346706</v>
       </c>
     </row>
     <row r="24">
@@ -993,19 +982,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.607565011820331</v>
+        <v>0.6705357142857142</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5943262411347517</v>
+        <v>0.6465608465608466</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7842857142857143</v>
+        <v>0.6445945945945946</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5923809523809523</v>
+        <v>0.6062350119904076</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6446394799054374</v>
+        <v>0.6419815418578907</v>
       </c>
     </row>
     <row r="25">
@@ -1016,31 +1005,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[94 47]
- [ 7  8]]</t>
+          <t>[[107, 33], [7, 9]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[99 42]
- [ 8  7]]</t>
+          <t>[[98, 37], [8, 6]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[105  35]
- [  5  10]]</t>
+          <t>[[94, 54], [7, 8]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[94 46]
- [ 9  6]]</t>
+          <t>[[99, 40], [8, 7]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[[98, 42], [7, 8]]</t>
+          <t>[[100, 41], [8, 8]]</t>
         </is>
       </c>
     </row>
@@ -1051,19 +1036,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8993288590604027</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9096774193548387</v>
+        <v>0.901840490797546</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8967741935483871</v>
+        <v>0.8896103896103896</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9003308519437552</v>
+        <v>0.8938487810209307</v>
       </c>
     </row>
     <row r="27">
@@ -1073,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4964539007092199</v>
+        <v>0.5205357142857143</v>
       </c>
       <c r="C27" t="n">
-        <v>0.526241134751773</v>
+        <v>0.4962962962962963</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5630952380952381</v>
+        <v>0.4966216216216216</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4964285714285714</v>
+        <v>0.4928057553956834</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5205547112462006</v>
+        <v>0.5015648468998289</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.472972972972973</v>
+        <v>0.5191780821917809</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5283446712018141</v>
+        <v>0.4734982332155477</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5871385083713851</v>
+        <v>0.4741935483870968</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4727891156462585</v>
+        <v>0.4707903780068728</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5153113170481077</v>
+        <v>0.4844150604503246</v>
       </c>
     </row>
     <row r="29">
@@ -1117,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8549896049896051</v>
+        <v>0.8523709167544783</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8653410081981511</v>
+        <v>0.858016932672469</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8814258359110325</v>
+        <v>0.8611122105679794</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8540706605222734</v>
+        <v>0.8498683447137055</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8639567774052656</v>
+        <v>0.855342101177158</v>
       </c>
     </row>
     <row r="30">
@@ -1139,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8456264775413712</v>
+        <v>0.7642857142857142</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7385342789598108</v>
+        <v>0.692063492063492</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8871428571428572</v>
+        <v>0.7558558558558559</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6835714285714286</v>
+        <v>0.7083932853717027</v>
       </c>
       <c r="F30" t="n">
-        <v>0.788718760553867</v>
+        <v>0.7301495868941913</v>
       </c>
     </row>
     <row r="31">
@@ -1162,31 +1147,413 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[140   1]
- [ 15   0]]</t>
+          <t>[[137, 3], [15, 1]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[139   2]
- [ 14   1]]</t>
+          <t>[[134, 1], [14, 0]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[139   1]
- [ 13   2]]</t>
+          <t>[[147, 1], [15, 0]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[139   1]
- [ 15   0]]</t>
+          <t>[[137, 2], [15, 0]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[139, 1], [14, 1]]</t>
+          <t>[[139, 2], [15, 0]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N_folds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_test</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acc_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bacc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bacc_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_sd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1_sd</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_sd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>conf_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tissue_Type_Clustering</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8968151938027797</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01429533203653117</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6262338247162887</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.08797320316602701</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.638225465983672</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.08666500491514113</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8854862048232217</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.02016116677070143</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7532275940830347</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.07908286595867027</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[[135, 6], [10, 4]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tissue_Type_Clustering</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>622</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7496308856115543</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01915439978501046</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6285555757453238</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.04695342876714454</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.559000108929147</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02989454252734346</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7930087347540028</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.01271801517907743</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.7028347109956822</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.02846236704848231</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[[109, 31], [8, 7]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tissue_Type_Clustering</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>622</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8972396442853889</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.008183550955269434</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5263701763814174</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.004670298664590299</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5287125008055565</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.007146487138331998</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8650224509718305</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.007623787527980923</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6079079569356098</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03855347401222068</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[[138, 2], [14, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tissue_Type_Clustering</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>622</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.688913720062071</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.04201092492697438</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6035810524681927</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.03480257188358607</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5212707031525863</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03447787745751926</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7494294819346706</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.02974890429810504</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6419815418578907</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.02302690402969994</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[[100, 41], [8, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tissue_Type_Clustering</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>622</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8938487810209307</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.007019940373736318</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5015648468998289</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01105450807322442</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4844150604503246</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02011066929526801</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.855342101177158</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.00445080983094973</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7301495868941913</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03061851863092898</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[[139, 2], [15, 0]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/SurGen_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,13 +616,13 @@
         <v>0.7516778523489933</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7177914110429447</v>
+        <v>0.7116564417177914</v>
       </c>
       <c r="E8" t="n">
         <v>0.7662337662337663</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7496308856115543</v>
+        <v>0.748097143280266</v>
       </c>
     </row>
     <row r="9">
@@ -638,13 +638,13 @@
         <v>0.5748677248677249</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6049549549549549</v>
+        <v>0.6015765765765766</v>
       </c>
       <c r="E9" t="n">
         <v>0.6326139088729017</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6285555757453238</v>
+        <v>0.6277109811507293</v>
       </c>
     </row>
     <row r="10">
@@ -660,13 +660,13 @@
         <v>0.5326777994405357</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5302005012531328</v>
+        <v>0.5260748530776369</v>
       </c>
       <c r="E10" t="n">
         <v>0.5702325581395349</v>
       </c>
       <c r="F10" t="n">
-        <v>0.559000108929147</v>
+        <v>0.5579686968852731</v>
       </c>
     </row>
     <row r="11">
@@ -682,13 +682,13 @@
         <v>0.7924719798515492</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7724295401079385</v>
+        <v>0.7680586892456815</v>
       </c>
       <c r="E11" t="n">
         <v>0.8039263062518877</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7930087347540028</v>
+        <v>0.7919160220384386</v>
       </c>
     </row>
     <row r="12">
@@ -704,13 +704,13 @@
         <v>0.665079365079365</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6869369369369369</v>
+        <v>0.6590090090090091</v>
       </c>
       <c r="E12" t="n">
         <v>0.7218225419664269</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7028347109956822</v>
+        <v>0.6958527290137002</v>
       </c>
     </row>
     <row r="13">
@@ -731,7 +731,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[110, 38], [8, 7]]</t>
+          <t>[[109, 39], [8, 7]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[109, 31], [8, 7]]</t>
+          <t>[[109, 32], [8, 7]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>622</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7496308856115543</v>
+        <v>0.748097143280266</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01915439978501046</v>
+        <v>0.0217167038853523</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6285555757453238</v>
+        <v>0.6277109811507293</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04695342876714454</v>
+        <v>0.04739863296104874</v>
       </c>
       <c r="J3" t="n">
-        <v>0.559000108929147</v>
+        <v>0.5579686968852731</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02989454252734346</v>
+        <v>0.03092383594840175</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7930087347540028</v>
+        <v>0.7919160220384386</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01271801517907743</v>
+        <v>0.01450187121247335</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7028347109956822</v>
+        <v>0.6958527290137002</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02846236704848231</v>
+        <v>0.03432705200357662</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[109, 31], [8, 7]]</t>
+          <t>[[109, 32], [8, 7]]</t>
         </is>
       </c>
     </row>
